--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487795_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487795_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0629</v>
+        <v>5.1678</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6124</v>
+        <v>4.5705</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4505</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>4.7011</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3836</v>
+        <v>0.4885</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4005</v>
+        <v>0.3586</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0169</v>
+        <v>0.1299</v>
       </c>
       <c r="V2" t="n">
         <v>-0.23</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.047</v>
+        <v>5.0741</v>
       </c>
       <c r="E3" t="n">
-        <v>5.712</v>
+        <v>5.5629</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.665</v>
+        <v>-0.4889</v>
       </c>
       <c r="G3" t="n">
         <v>6.0942</v>
@@ -688,13 +688,13 @@
         <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0254</v>
+        <v>0.0017</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5434</v>
+        <v>0.3944</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5689</v>
+        <v>-0.3927</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8137</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1771</v>
+        <v>4.4017</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3114</v>
+        <v>3.4185</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8657</v>
+        <v>0.9832</v>
       </c>
       <c r="G4" t="n">
         <v>1.9229</v>
@@ -766,13 +766,13 @@
         <v>0.6244</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1422</v>
+        <v>0.0824</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0776</v>
+        <v>0.1848</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2198</v>
+        <v>-0.1024</v>
       </c>
       <c r="V4" t="n">
         <v>2.8127</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8808</v>
+        <v>3.7992</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7975</v>
+        <v>2.8628</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0833</v>
+        <v>0.9365</v>
       </c>
       <c r="G5" t="n">
         <v>3.0652</v>
@@ -844,13 +844,13 @@
         <v>2.2893</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.5259</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4129</v>
+        <v>0.4782</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1945</v>
+        <v>0.0477</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4852</v>
+        <v>3.5966</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8375</v>
+        <v>4.8608</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3524</v>
+        <v>-1.2643</v>
       </c>
       <c r="G6" t="n">
         <v>3.0074</v>
@@ -922,13 +922,13 @@
         <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3321</v>
+        <v>0.4435</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4129</v>
+        <v>0.4363</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0809</v>
+        <v>0.0072</v>
       </c>
       <c r="V6" t="n">
         <v>0.3538</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0165</v>
+        <v>1.6443</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2688</v>
+        <v>0.2217</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2524</v>
+        <v>1.4226</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2623</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1815</v>
+        <v>-1.729</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0808</v>
+        <v>1.1479</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7036</v>
+        <v>0.3744</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0554</v>
+        <v>-0.949</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6482</v>
+        <v>1.3234</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4412</v>
+        <v>-0.9555</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8738</v>
+        <v>-0.78</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5674</v>
+        <v>-0.1755</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>2.2893</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4836</v>
+        <v>0.6198</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3759</v>
+        <v>0.531</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1077</v>
+        <v>0.0888</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3538</v>
+        <v>1.3975</v>
       </c>
       <c r="W7" t="n">
-        <v>0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5203</v>
+        <v>1.3903</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1565</v>
+        <v>1.584</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3639</v>
+        <v>-0.1937</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5810999999999999</v>
+        <v>0.2623</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.729</v>
+        <v>0.1815</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1479</v>
+        <v>0.0808</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3744</v>
+        <v>1.7036</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.949</v>
+        <v>1.0554</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3234</v>
+        <v>0.6482</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9555</v>
+        <v>-1.4412</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.78</v>
+        <v>-0.8738</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1755</v>
+        <v>-0.5674</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2893</v>
+        <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4958</v>
+        <v>0.8575</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4658</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0301</v>
+        <v>0.1664</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3975</v>
+        <v>-0.3538</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3733</v>
+        <v>0.0134</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7199</v>
+        <v>-1.3332</v>
       </c>
       <c r="F9" t="n">
         <v>1.3466</v>
@@ -1156,10 +1156,10 @@
         <v>2.2893</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4658</v>
+        <v>-0.0791</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2486</v>
+        <v>0.1381</v>
       </c>
       <c r="U9" t="n">
         <v>-0.2172</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2193</v>
+        <v>-1.1121</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8517</v>
+        <v>-0.7446</v>
       </c>
       <c r="F10" t="n">
         <v>-0.3675</v>
@@ -1234,10 +1234,10 @@
         <v>0.2081</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3386</v>
+        <v>-0.2314</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="U10" t="n">
         <v>-0.1429</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5659</v>
+        <v>-1.8046</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7303</v>
+        <v>-3.5579</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1644</v>
+        <v>1.7534</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6709000000000001</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7699</v>
+        <v>0.5312</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2824</v>
+        <v>0.4548</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4874</v>
+        <v>0.0764</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3772</v>
+        <v>-1.8643</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.223</v>
+        <v>-2.622</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8458</v>
+        <v>0.7577</v>
       </c>
       <c r="G12" t="n">
         <v>1.2066</v>
@@ -1390,13 +1390,13 @@
         <v>0.8325</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0998</v>
+        <v>0.6128</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2362</v>
+        <v>0.3648</v>
       </c>
       <c r="U12" t="n">
-        <v>0.336</v>
+        <v>0.248</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3538</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>19.6541</v>
+        <v>20.3064</v>
       </c>
       <c r="E13" t="n">
-        <v>14.17120000000001</v>
+        <v>14.8235</v>
       </c>
       <c r="F13" t="n">
-        <v>5.482899999999999</v>
+        <v>5.482900000000001</v>
       </c>
       <c r="G13" t="n">
         <v>18.5931</v>
@@ -1450,7 +1450,7 @@
         <v>14.5729</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.860300000000001</v>
+        <v>-5.8603</v>
       </c>
       <c r="N13" t="n">
         <v>-6.595299999999999</v>
@@ -1459,7 +1459,7 @@
         <v>0.7349</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.2435</v>
+        <v>-6.243499999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-21.8526</v>
@@ -1468,13 +1468,13 @@
         <v>15.6089</v>
       </c>
       <c r="S13" t="n">
-        <v>3.200200000000001</v>
+        <v>3.8528</v>
       </c>
       <c r="T13" t="n">
-        <v>3.290899999999999</v>
+        <v>3.9434</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.09089999999999998</v>
+        <v>-0.0908000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>4.104100000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. CHABI YO</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4252</v>
+        <v>0.2523</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1957</v>
+        <v>4.1366</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2294</v>
+        <v>-3.8842</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.249</v>
+        <v>-1.5409</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.3197</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.249</v>
+        <v>-1.8606</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2.9415</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1.8141</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.1275</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.249</v>
+        <v>-4.4824</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-1.4943</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.249</v>
+        <v>-2.9881</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.0812</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.1218</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1762</v>
+        <v>0.0659</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1957</v>
+        <v>0.2544</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0196</v>
+        <v>-0.1885</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.9813</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>J. JIMÉNEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4327</v>
+        <v>0.1519</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7079</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.1406</v>
+        <v>-0.4373</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.5409</v>
+        <v>-3.3304</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3197</v>
+        <v>-0.4582</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8606</v>
+        <v>-2.8722</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9415</v>
+        <v>0.4173</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8141</v>
+        <v>1.228</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1275</v>
+        <v>-0.8107</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.4824</v>
+        <v>-3.7477</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4943</v>
+        <v>-1.6862</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.9881</v>
+        <v>-2.0614</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0812</v>
+        <v>3.538</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1218</v>
+        <v>3.538</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6192</v>
+        <v>-0.5228</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1743</v>
+        <v>-0.4119</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4449</v>
+        <v>-0.1109</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3538</v>
+        <v>0.467</v>
       </c>
       <c r="W15" t="n">
-        <v>1.9813</v>
+        <v>0.5838</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.3351</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6603</v>
+        <v>-0.0785</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3522</v>
+        <v>1.6737</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0125</v>
+        <v>-1.7522</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4995</v>
@@ -1702,13 +1702,13 @@
         <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.2253</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3791</v>
+        <v>-0.0576</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.428</v>
+        <v>-0.1677</v>
       </c>
       <c r="V16" t="n">
         <v>0.23</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>S. CHABI YO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1149</v>
+        <v>-0.3958</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1609</v>
+        <v>-0.1957</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.954</v>
+        <v>-0.2001</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.3304</v>
+        <v>-0.249</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4582</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.8722</v>
+        <v>-0.249</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4173</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.8107</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.7477</v>
+        <v>-0.249</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6862</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.0614</v>
+        <v>-0.249</v>
       </c>
       <c r="P17" t="n">
-        <v>3.538</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.538</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7896</v>
+        <v>-0.1468</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.162</v>
+        <v>-0.1957</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6276</v>
+        <v>0.0489</v>
       </c>
       <c r="V17" t="n">
-        <v>0.467</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>J. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1729</v>
+        <v>-0.9997</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5377999999999999</v>
+        <v>-0.1956</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7107</v>
+        <v>-0.8041</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.5938</v>
+        <v>-0.1149</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8597</v>
+        <v>0.5007</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7341</v>
+        <v>-0.6156</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5769</v>
+        <v>2.3998</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6553</v>
+        <v>1.2724</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0784</v>
+        <v>1.1275</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.0169</v>
+        <v>-2.5147</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2044</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8124</v>
+        <v>-1.7431</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8731</v>
+        <v>0.2081</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9137</v>
+        <v>2.2893</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0184</v>
+        <v>-0.633</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1116</v>
+        <v>-0.5143</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.1187</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.4706</v>
+        <v>-0.4599</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0437</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5142</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6676</v>
+        <v>-1.9499</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.747</v>
+        <v>-0.3194</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0795</v>
+        <v>-1.6305</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.4067</v>
+        <v>-3.5938</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.4864</v>
+        <v>-1.8597</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9202</v>
+        <v>-1.7341</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.9614</v>
+        <v>-0.5769</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.5719</v>
+        <v>-0.6553</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3896</v>
+        <v>0.0784</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4452</v>
+        <v>-3.0169</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9145</v>
+        <v>-1.2044</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-1.8124</v>
       </c>
       <c r="P19" t="n">
-        <v>1.4568</v>
+        <v>1.8731</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4568</v>
+        <v>2.9137</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0523</v>
+        <v>0.2414</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.2544</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0679</v>
+        <v>-0.013</v>
       </c>
       <c r="V19" t="n">
-        <v>0.23</v>
+        <v>-0.4706</v>
       </c>
       <c r="W19" t="n">
-        <v>0.23</v>
+        <v>1.0437</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.5142</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MARIN ORTEGA</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7537</v>
+        <v>-2.0707</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5171</v>
+        <v>-2.1757</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2366</v>
+        <v>0.1049</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1149</v>
+        <v>-4.4067</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5007</v>
+        <v>-2.4864</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6156</v>
+        <v>-1.9202</v>
       </c>
       <c r="J20" t="n">
-        <v>2.3998</v>
+        <v>-2.9614</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2724</v>
+        <v>-1.5719</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1275</v>
+        <v>-1.3896</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5147</v>
+        <v>-1.4452</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.9145</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7431</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2081</v>
+        <v>1.4568</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2893</v>
+        <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.387</v>
+        <v>0.6491</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8358</v>
+        <v>0.5558</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5513</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4599</v>
+        <v>0.23</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8887</v>
+        <v>-3.3696</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-1.2882</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1362</v>
+        <v>-2.0814</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5991</v>
@@ -2092,13 +2092,13 @@
         <v>2.0812</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4723</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9968</v>
+        <v>0.461</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5245</v>
+        <v>-0.4697</v>
       </c>
       <c r="V21" t="n">
         <v>-1.7619</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6578</v>
+        <v>-4.3427</v>
       </c>
       <c r="E22" t="n">
         <v>-4.3792</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2786</v>
+        <v>0.0365</v>
       </c>
       <c r="G22" t="n">
         <v>-3.4707</v>
@@ -2170,13 +2170,13 @@
         <v>2.4974</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.319</v>
+        <v>-0.0039</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0562</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2629</v>
+        <v>0.0522</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2843</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8803</v>
+        <v>-4.7081</v>
       </c>
       <c r="E23" t="n">
         <v>-3.3283</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.552</v>
+        <v>-1.3797</v>
       </c>
       <c r="G23" t="n">
         <v>0.2116</v>
@@ -2248,13 +2248,13 @@
         <v>2.4974</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6452</v>
+        <v>-0.473</v>
       </c>
       <c r="T23" t="n">
         <v>-0.199</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4462</v>
+        <v>-0.274</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7005</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-19.6541</v>
+        <v>-17.5108</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4828</v>
+        <v>-5.482600000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-14.1711</v>
+        <v>-12.0281</v>
       </c>
       <c r="G24" t="n">
         <v>-18.5934</v>
@@ -2302,7 +2302,7 @@
         <v>5.8604</v>
       </c>
       <c r="K24" t="n">
-        <v>6.5953</v>
+        <v>6.595299999999999</v>
       </c>
       <c r="L24" t="n">
         <v>-0.7347000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>21.8524</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.2002</v>
+        <v>-1.0571</v>
       </c>
       <c r="T24" t="n">
-        <v>0.09070000000000028</v>
+        <v>0.09089999999999993</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.291100000000001</v>
+        <v>-1.1481</v>
       </c>
       <c r="V24" t="n">
         <v>-4.104</v>
